--- a/artfynd/A 41966-2022 artfynd.xlsx
+++ b/artfynd/A 41966-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41966-2022 artfynd.xlsx
+++ b/artfynd/A 41966-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1651,7 +1651,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112607054</v>
+        <v>112610516</v>
       </c>
       <c r="B10" t="n">
         <v>77608</v>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>389934</v>
+        <v>389935</v>
       </c>
       <c r="R10" t="n">
-        <v>6854163</v>
+        <v>6854165</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1755,113 +1755,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>112610516</v>
-      </c>
-      <c r="B11" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Älvros, Dlr</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>389935</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6854165</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Särna</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
